--- a/output/北塩原村_報告書レビュー反映版の確認.xlsx
+++ b/output/北塩原村_報告書レビュー反映版の確認.xlsx
@@ -3831,7 +3831,7 @@
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>レビューの結果を反映いただいた報告書を拝見しました。前の文を消さずに新しい文を重ねたとみられる箇所が11か所あり、日本語が崩れています（「、、」「ありとなっており」「もという回答も」「のに基づく」など）。いずれも内容の誤りではなく機械的に直せるものですが、報告書は策定委員会に出す資料であるため、お戻しいたします。箇所と直し方は「北塩原村_報告書レビュー反映版の確認.xlsx」の02シートに一覧にしています。このうち2か所は意図の確認が要ります。①障がい児調査の「移動支援」「移動に関する支援」はどちらを残されますか。②課題3の「避難所における安全性と合理的配慮のに基づく支え合いの提供体制」は、「安全性」と「支え合い」でそれぞれ何を指しておられますか。なお、変更履歴とコメントは残っておらず、ファイルの作成日時が改訂時にリセットされています。次回以降、変更履歴を付けたままお送りいただけますと、どの指摘への対応かが分かり助かります。</t>
+          <t>レビューの結果を反映いただいた報告書を拝見しました。前の文を消さずに新しい文を重ねたとみられる箇所が11か所あり、日本語が崩れています（「、、」「ありとなっており」「もという回答も」「のに基づく」など）。いずれも内容の誤りではなく機械的に直せるものですが、報告書は策定委員会に出す資料であるため、お戻しいたします。箇所は「北塩原村_報告書レビュー反映版の確認.xlsx」の02シートに一覧にしており、そのまま適用できる形の置換文を「北塩原村_報告書の修正方針と計画への影響.xlsx」の02シートにお付けしています。このうち1か所は意図の確認が要ります。課題3の「避難所における安全性と合理的配慮のに基づく支え合いの提供体制」は、「安全性」と「支え合い」でそれぞれ何を指しておられますか。なお障がい児調査の「移動支援」「移動に関する支援」は、問29の選択肢名が「移動支援」であることを集計表で確かめましたので、「移動支援」とする案をお示ししています。なお、変更履歴とコメントは残っておらず、ファイルの作成日時が改訂時にリセットされています。次回以降、変更履歴を付けたままお送りいただけますと、どの指摘への対応かが分かり助かります。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">

--- a/output/北塩原村_報告書レビュー反映版の確認.xlsx
+++ b/output/北塩原村_報告書レビュー反映版の確認.xlsx
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>P963（2）</t>
+          <t>P965（2）</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>P965（1）</t>
+          <t>P967（1）</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>P793（2）</t>
+          <t>P795（2）</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>P978（1）</t>
+          <t>P980（1）</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>P977（1）</t>
+          <t>P979（1）</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>P978（2）</t>
+          <t>P980（2）</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>P292（7）</t>
+          <t>P292（8）</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>P949（4）</t>
+          <t>P951（4）</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>P1073（2）</t>
+          <t>P1075（2）</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>P978（1）</t>
+          <t>P980（1）</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>P963（2）</t>
+          <t>P965（2）</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>P963（2）</t>
+          <t>P965（2）</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>ユニバーサルデザイン</t>
+          <t>スロープ</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>公共施設の整備は第4次障がい者計画の取組みであり、本計画は表3-1⑥の目標値（公共施設トイレの設置率）により進捗を確かめる</t>
+          <t>公共施設の整備は第4次障がい者計画の取組みであり、本計画は表3-1⑥の目標値（公共施設トイレの設置率）により進捗を確かめる。なおユニバーサルデザインの考え方のうち広報に関わる部分（ＵＤフォント・文字の大きさ・配色）は令和8年10月22日に正本へ入れた（ＳＺ-3）</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_報告書レビュー反映版の確認.xlsx
+++ b/output/北塩原村_報告書レビュー反映版の確認.xlsx
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>P965（2）</t>
+          <t>P970（2）</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>P967（1）</t>
+          <t>P972（1）</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>P792（5）</t>
+          <t>P796（5）</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>P795（2）</t>
+          <t>P799（2）</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>P980（1）</t>
+          <t>P985（1）</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>P791（2）</t>
+          <t>P795（2）</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>P979（1）</t>
+          <t>P984（1）</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>P980（2）</t>
+          <t>P985（2）</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>P666（20）</t>
+          <t>P666（21）</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>P502（32）</t>
+          <t>P502（33）</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>P951（4）</t>
+          <t>P955（4）</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>P1075（2）</t>
+          <t>P1080（2）</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>P779（4）</t>
+          <t>P783（4）</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>P779（1）</t>
+          <t>P783（1）</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>P980（1）</t>
+          <t>P985（1）</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>P965（2）</t>
+          <t>P970（2）</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>P965（2）</t>
+          <t>P970（2）</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>T114.1.1（1）</t>
+          <t>T118.1.1（1）</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>P792（3）</t>
+          <t>P796（3）</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">

--- a/output/北塩原村_報告書レビュー反映版の確認.xlsx
+++ b/output/北塩原村_報告書レビュー反映版の確認.xlsx
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>P970（2）</t>
+          <t>P972（2）</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>P972（1）</t>
+          <t>P974（1）</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>P796（5）</t>
+          <t>P798（5）</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>P538（11）</t>
+          <t>P539（11）</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>P799（2）</t>
+          <t>P801（2）</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>P985（1）</t>
+          <t>P987（1）</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>P795（2）</t>
+          <t>P797（2）</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>P984（1）</t>
+          <t>P986（1）</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>P985（2）</t>
+          <t>P987（2）</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>T72.4.0（2）</t>
+          <t>T73.4.0（2）</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>P666（21）</t>
+          <t>P667（22）</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>P502（33）</t>
+          <t>P502（34）</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>P955（4）</t>
+          <t>P957（4）</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>P547（15）</t>
+          <t>P548（15）</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>P1080（2）</t>
+          <t>P1082（2）</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>P783（4）</t>
+          <t>P785（4）</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>P783（1）</t>
+          <t>P785（1）</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>P985（1）</t>
+          <t>P987（1）</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>P970（2）</t>
+          <t>P972（2）</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>P970（2）</t>
+          <t>P972（2）</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>P528（2）</t>
+          <t>P529（2）</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>P468（20）</t>
+          <t>P468（21）</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>T118.1.1（1）</t>
+          <t>T120.1.1（1）</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>P796（3）</t>
+          <t>P798（3）</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">

--- a/output/北塩原村_報告書レビュー反映版の確認.xlsx
+++ b/output/北塩原村_報告書レビュー反映版の確認.xlsx
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>P972（2）</t>
+          <t>P973（2）</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>P974（1）</t>
+          <t>P975（1）</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>P798（5）</t>
+          <t>P799（5）</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>P801（2）</t>
+          <t>P802（2）</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>P987（1）</t>
+          <t>P988（1）</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>P797（2）</t>
+          <t>P798（2）</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>P986（1）</t>
+          <t>P987（1）</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>P987（2）</t>
+          <t>P988（2）</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>P957（4）</t>
+          <t>P958（4）</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>P1082（2）</t>
+          <t>P1083（2）</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>P987（1）</t>
+          <t>P988（1）</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>P972（2）</t>
+          <t>P973（2）</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>P972（2）</t>
+          <t>P973（2）</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>T120.1.1（1）</t>
+          <t>T121.1.1（1）</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>P798（3）</t>
+          <t>P799（3）</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
